--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16965" windowHeight="13155"/>
+    <workbookView windowWidth="13230" windowHeight="9645"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1212,7 +1212,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>17</v>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13230" windowHeight="9645"/>
+    <workbookView windowWidth="11535" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -61,7 +61,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>HeroEntryType</t>
+    <t>MechanismType</t>
   </si>
   <si>
     <t>float</t>
@@ -82,7 +82,7 @@
     <t>大壮</t>
   </si>
   <si>
-    <t>AStrongPerson</t>
+    <t>HeroTakeDamagePer</t>
   </si>
   <si>
     <t>受到的伤害-25%</t>
@@ -91,10 +91,19 @@
     <t>狠人</t>
   </si>
   <si>
-    <t>Badass</t>
-  </si>
-  <si>
-    <t>造成的伤害+25%</t>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>造成的伤害+20%</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>拥有15%暴击率</t>
   </si>
   <si>
     <t>多面手</t>
@@ -103,58 +112,91 @@
     <t>VersatilePerson</t>
   </si>
   <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>攻击时,对其他敌人造成30%的伤害</t>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>攻击时,对其他人造成25%的伤害</t>
   </si>
   <si>
     <t>射手</t>
   </si>
   <si>
-    <t>Archer</t>
-  </si>
-  <si>
-    <t>攻击时,有50%概率额外进行一次攻击</t>
+    <t>ExtraAttackOneTime</t>
+  </si>
+  <si>
+    <t>攻击时,有25%概率额外攻击1次</t>
   </si>
   <si>
     <t>大嗓门</t>
   </si>
   <si>
-    <t>LoudVoice</t>
-  </si>
-  <si>
-    <t>攻击时,对所有人造成1次原伤害50%的群体伤害</t>
+    <t>AoeDamage</t>
+  </si>
+  <si>
+    <t>攻击时,对所有人造成30%的群体伤害</t>
+  </si>
+  <si>
+    <t>富豪</t>
+  </si>
+  <si>
+    <t>InitialFunds</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>初始额外拥有30金币</t>
+  </si>
+  <si>
+    <t>武林高手</t>
+  </si>
+  <si>
+    <t>MissDamagePer</t>
+  </si>
+  <si>
+    <t>承受伤害时有20%概率免疫伤害</t>
+  </si>
+  <si>
+    <t>赌神</t>
+  </si>
+  <si>
+    <t>RubbingCardsNum</t>
+  </si>
+  <si>
+    <t>额外拥有1次搓牌机会</t>
   </si>
   <si>
     <t>暴发户</t>
   </si>
   <si>
-    <t>NouveauRiche</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>初始拥有100资金</t>
-  </si>
-  <si>
-    <t>流浪汉</t>
-  </si>
-  <si>
-    <t>HomelessPerson</t>
-  </si>
-  <si>
-    <t>在闷注获胜后,获得的积分数量+100%</t>
-  </si>
-  <si>
-    <t>赌神</t>
-  </si>
-  <si>
-    <t>GodOfGamblers</t>
-  </si>
-  <si>
-    <t>拿到非散牌的概率提高30%</t>
+    <t>EpicLegendRelicProUp</t>
+  </si>
+  <si>
+    <t>商店刷到史诗及以上品质的收藏品概率+15%</t>
+  </si>
+  <si>
+    <t>关系户</t>
+  </si>
+  <si>
+    <t>RelicPricePer</t>
+  </si>
+  <si>
+    <t>-0.15</t>
+  </si>
+  <si>
+    <t>商店中的所有收藏品的购买价格-15%</t>
+  </si>
+  <si>
+    <t>经济教授</t>
+  </si>
+  <si>
+    <t>GetGoldAfterLevel</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>每关通过后获得的金币数量+20%</t>
   </si>
 </sst>
 </file>
@@ -1128,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1208,11 +1250,11 @@
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.2</v>
+        <v>-0.25</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>17</v>
@@ -1230,42 +1272,42 @@
         <v>19</v>
       </c>
       <c r="E6" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" customFormat="1" spans="1:6">
+      <c r="A7" s="1"/>
       <c r="B7" s="2">
+        <v>100021</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="2">
         <v>10003</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:6">
-      <c r="A8" s="1"/>
-      <c r="B8" s="2">
-        <v>10004</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>27</v>
@@ -1274,7 +1316,7 @@
     <row r="9" customFormat="1" spans="1:6">
       <c r="A9" s="1"/>
       <c r="B9" s="2">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
@@ -1283,42 +1325,42 @@
         <v>29</v>
       </c>
       <c r="E9" s="2">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" customFormat="1" spans="1:6">
+      <c r="A10" s="1"/>
       <c r="B10" s="2">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="1" t="s">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:6">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2">
-        <v>10007</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>37</v>
@@ -1327,7 +1369,7 @@
     <row r="12" customFormat="1" spans="1:6">
       <c r="A12" s="1"/>
       <c r="B12" s="2">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>38</v>
@@ -1336,10 +1378,97 @@
         <v>39</v>
       </c>
       <c r="E12" s="2">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
+      <c r="A13" s="1"/>
+      <c r="B13" s="2">
+        <v>100071</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2">
+        <v>10008</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="2">
+        <v>10009</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="2">
+        <v>10010</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="2">
+        <v>10011</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -1043,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="1"/>
@@ -1455,6 +1455,259 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>10012</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>英雄13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AttackBossDamage</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>对精英、领主造成的伤害+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>10013</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>英雄14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>KillingProbabilityTen</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>对血量小于10%的非领主敌人造成伤害时,有20%概率直接斩杀</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>10014</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>英雄15</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HpUnderDamage</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>自身血量小于20%时,造成的伤害+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>10015</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>英雄16</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RelicNumMax</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>圣物携带上限+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>10016</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>英雄17</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PerspectiveNum</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>每关[透视]使用次数+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>10017</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>英雄18</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HeroHpReplyEveryLevelEnding</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>每次通关后额外回复自身10%血量</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>10018</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>英雄19</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>KillingGetGold</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>每击杀1名敌人,额外获得20金币</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>10019</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>英雄20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>KillingGetAttack</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>每击杀1名敌人,额外提高2点攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>10020</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>英雄21</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OneMonsterDamage</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>场上只剩1名敌人时,造成的伤害+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>10021</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>英雄22</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ManyMonsterDamage</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>场上敌人多于1名时,造成的伤害+30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>10022</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>英雄23</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FirstShowCardEveryLevel</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>每关第一轮比牌时,结算时的倍率+2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15285" windowHeight="12825"/>
+    <workbookView windowWidth="15285" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -95,15 +95,6 @@
   </si>
   <si>
     <t>造成的伤害+25%</t>
-  </si>
-  <si>
-    <t>HeroCritical</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>拥有15%暴击率</t>
   </si>
   <si>
     <t>多面手</t>
@@ -908,12 +899,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1275,285 +1263,285 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="7.71666666666667" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.34166666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.825" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.71666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.34166666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.825" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>10001</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>-0.25</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>10002</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>0.25</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="3">
-        <v>100021</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="B7" s="2">
+        <v>10003</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="3">
-        <v>10003</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="2">
+        <v>10004</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="2" t="s">
+        <v>0.35</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="3">
-        <v>10004</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="2">
+        <v>10005</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="3">
-        <v>10005</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="E10" s="1">
+        <v>150</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="B11" s="3">
-        <v>10006</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B11" s="2">
+        <v>10007</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>34</v>
       </c>
       <c r="E11" s="2">
-        <v>150</v>
-      </c>
-      <c r="F11" s="2" t="s">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="B12" s="3">
-        <v>10007</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="2">
+        <v>10008</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="B13" s="3">
-        <v>10008</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B13" s="2">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>41</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="B14" s="3">
-        <v>10009</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B14" s="2">
+        <v>10010</v>
+      </c>
+      <c r="C14" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="B15" s="3">
-        <v>10010</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="2">
+        <v>10011</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="2">
-        <v>-0.2</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="B16" s="3">
-        <v>10011</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="2">
+        <v>10012</v>
+      </c>
+      <c r="C16" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" t="s">
         <v>50</v>
       </c>
       <c r="E16" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="2" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="3">
-        <v>10012</v>
+      <c r="B17" s="2">
+        <v>10013</v>
       </c>
       <c r="C17" t="s">
         <v>52</v>
@@ -1561,16 +1549,16 @@
       <c r="D17" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="3">
-        <v>0.5</v>
+      <c r="E17" s="2">
+        <v>0.2</v>
       </c>
       <c r="F17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="3">
-        <v>10013</v>
+      <c r="B18" s="2">
+        <v>10014</v>
       </c>
       <c r="C18" t="s">
         <v>55</v>
@@ -1578,16 +1566,16 @@
       <c r="D18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="3">
-        <v>0.2</v>
+      <c r="E18" s="2">
+        <v>0.5</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="3">
-        <v>10014</v>
+      <c r="B19" s="2">
+        <v>10015</v>
       </c>
       <c r="C19" t="s">
         <v>58</v>
@@ -1595,16 +1583,16 @@
       <c r="D19" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="3">
-        <v>0.5</v>
+      <c r="E19" s="2">
+        <v>1</v>
       </c>
       <c r="F19" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="3">
-        <v>10015</v>
+      <c r="B20" s="2">
+        <v>10016</v>
       </c>
       <c r="C20" t="s">
         <v>61</v>
@@ -1612,7 +1600,7 @@
       <c r="D20" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>1</v>
       </c>
       <c r="F20" t="s">
@@ -1621,42 +1609,42 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="3">
-        <v>10016</v>
-      </c>
-      <c r="C21" t="s">
+        <v>10017</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E21" s="3">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
+        <v>0.02</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="4">
-        <v>10017</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="2">
+        <v>10018</v>
+      </c>
+      <c r="C22" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>68</v>
       </c>
-      <c r="E22" s="4">
-        <v>0.02</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="E22" s="2">
+        <v>20</v>
+      </c>
+      <c r="F22" t="s">
         <v>69</v>
       </c>
-      <c r="G22" s="5"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="3">
-        <v>10018</v>
+      <c r="B23" s="2">
+        <v>10019</v>
       </c>
       <c r="C23" t="s">
         <v>70</v>
@@ -1664,16 +1652,16 @@
       <c r="D23" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="3">
-        <v>20</v>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="3">
-        <v>10019</v>
+      <c r="B24" s="2">
+        <v>10020</v>
       </c>
       <c r="C24" t="s">
         <v>73</v>
@@ -1681,16 +1669,16 @@
       <c r="D24" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="3">
-        <v>2</v>
+      <c r="E24" s="2">
+        <v>0.5</v>
       </c>
       <c r="F24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="3">
-        <v>10020</v>
+      <c r="B25" s="2">
+        <v>10021</v>
       </c>
       <c r="C25" t="s">
         <v>76</v>
@@ -1698,16 +1686,16 @@
       <c r="D25" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="3">
-        <v>0.5</v>
+      <c r="E25" s="2">
+        <v>0.3</v>
       </c>
       <c r="F25" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="3">
-        <v>10021</v>
+      <c r="B26" s="2">
+        <v>10022</v>
       </c>
       <c r="C26" t="s">
         <v>79</v>
@@ -1715,28 +1703,11 @@
       <c r="D26" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="3">
-        <v>0.3</v>
+      <c r="E26" s="2">
+        <v>5</v>
       </c>
       <c r="F26" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="3">
-        <v>10022</v>
-      </c>
-      <c r="C27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="3">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15285" windowHeight="11655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1266,7 +1266,7 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.325" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.71666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.34166666666667" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.825" style="2" customWidth="1"/>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="84">
   <si>
     <t>##var</t>
   </si>
@@ -64,7 +64,7 @@
     <t>MechanismType</t>
   </si>
   <si>
-    <t>float</t>
+    <t>float[]</t>
   </si>
   <si>
     <t>效果名字</t>
@@ -79,205 +79,211 @@
     <t>描述</t>
   </si>
   <si>
-    <t>大壮</t>
+    <t>承伤</t>
   </si>
   <si>
     <t>HeroTakeDamagePer</t>
   </si>
   <si>
+    <t>受到的伤害+25%</t>
+  </si>
+  <si>
+    <t>攻击追击</t>
+  </si>
+  <si>
+    <t>ExtraAttackOneTime</t>
+  </si>
+  <si>
+    <t>攻击时,有35%概率追加攻击1次</t>
+  </si>
+  <si>
+    <t>分裂基础伤害</t>
+  </si>
+  <si>
+    <t>VersatilePerson</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>攻击时,对其他人造成10%的分裂伤害</t>
+  </si>
+  <si>
+    <t>分裂伤害提高</t>
+  </si>
+  <si>
+    <t>VersatilePersonUp</t>
+  </si>
+  <si>
+    <t>1|0.03|0.06</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人分裂伤害提高3%(精英/领主提高6%)</t>
+  </si>
+  <si>
+    <t>无法暴击</t>
+  </si>
+  <si>
+    <t>UnableCritical</t>
+  </si>
+  <si>
+    <t>降低血量获得伤害</t>
+  </si>
+  <si>
+    <t>GainDamageUpWhenHpDecreases</t>
+  </si>
+  <si>
+    <t>80|0.05|20</t>
+  </si>
+  <si>
+    <t>每降低80血量都会使伤害提高5%,最多叠加20层</t>
+  </si>
+  <si>
+    <t>吸血效果</t>
+  </si>
+  <si>
+    <t>BloodSucking</t>
+  </si>
+  <si>
+    <t>攻击造成8%的吸血</t>
+  </si>
+  <si>
+    <t>无法通过圣物回复</t>
+  </si>
+  <si>
+    <t>UnableReplyHp</t>
+  </si>
+  <si>
+    <t>杀敌提高攻击力</t>
+  </si>
+  <si>
+    <t>KillingGetAttack</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,提高3点攻击力</t>
+  </si>
+  <si>
+    <t>攻击力达到一定值变为群体伤害</t>
+  </si>
+  <si>
+    <t>AoeDamageWhenAttack</t>
+  </si>
+  <si>
+    <t>攻击力达到150时,攻击变为群体伤害</t>
+  </si>
+  <si>
+    <t>强力敌人伤害</t>
+  </si>
+  <si>
+    <t>AttackBossDamage</t>
+  </si>
+  <si>
+    <t>对精英/领主造成的伤害-25%</t>
+  </si>
+  <si>
+    <t>群体伤害</t>
+  </si>
+  <si>
+    <t>AoeDamage</t>
+  </si>
+  <si>
+    <t>攻击时,对所有人造成40%的群体伤害</t>
+  </si>
+  <si>
+    <t>对精英/领主造成的伤害+50%</t>
+  </si>
+  <si>
+    <t>提高圣物回复效果</t>
+  </si>
+  <si>
+    <t>RelicReplyHp</t>
+  </si>
+  <si>
+    <t>通过圣物获得的生命回复效果+50%</t>
+  </si>
+  <si>
+    <t>敌人数量的倍数伤害</t>
+  </si>
+  <si>
+    <t>MonsterNumDamage</t>
+  </si>
+  <si>
+    <t>每回合开始时会受到场上当前敌人数量*2的伤害</t>
+  </si>
+  <si>
     <t>受到的伤害-25%</t>
   </si>
   <si>
-    <t>狠人</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>造成的伤害+25%</t>
-  </si>
-  <si>
-    <t>多面手</t>
-  </si>
-  <si>
-    <t>VersatilePerson</t>
-  </si>
-  <si>
-    <t>攻击时,对其他人造成30%的伤害</t>
-  </si>
-  <si>
-    <t>射手</t>
-  </si>
-  <si>
-    <t>ExtraAttackOneTime</t>
-  </si>
-  <si>
-    <t>攻击时,有35%概率额外攻击1次</t>
-  </si>
-  <si>
-    <t>大嗓门</t>
-  </si>
-  <si>
-    <t>AoeDamage</t>
-  </si>
-  <si>
-    <t>攻击时,对所有人造成40%的群体伤害</t>
-  </si>
-  <si>
-    <t>富豪</t>
-  </si>
-  <si>
-    <t>InitialFunds</t>
-  </si>
-  <si>
-    <t>初始额外拥有150金币</t>
-  </si>
-  <si>
-    <t>武林高手</t>
+    <t>圣光燃烧</t>
+  </si>
+  <si>
+    <t>HolyLightBurning</t>
+  </si>
+  <si>
+    <t>1|0.5|0.1</t>
+  </si>
+  <si>
+    <t>每回合开始会发动1次[圣光燃烧],亮牌时是对子牌型且获得胜利,也会发动[圣光燃烧](对场上所有敌人造成1次圣骑士当前攻击力50%的伤害,每发动1次会使后续攻击力给予伤害+10%)</t>
+  </si>
+  <si>
+    <t>无法闪避</t>
+  </si>
+  <si>
+    <t>UnableMissing</t>
+  </si>
+  <si>
+    <t>圣物价格</t>
+  </si>
+  <si>
+    <t>RelicPricePer</t>
+  </si>
+  <si>
+    <t>商店中所有圣物的购买价格-20%</t>
+  </si>
+  <si>
+    <t>杀敌获得金币</t>
+  </si>
+  <si>
+    <t>KillingGetGold</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,额外获得50金币</t>
+  </si>
+  <si>
+    <t>无法通过圣物效果获得金币</t>
+  </si>
+  <si>
+    <t>UnableReplyGetGold</t>
+  </si>
+  <si>
+    <t>闪避概率</t>
   </si>
   <si>
     <t>MissDamagePer</t>
   </si>
   <si>
-    <t>承受伤害时有25%概率免疫伤害</t>
-  </si>
-  <si>
-    <t>赌神</t>
+    <t>获得50%闪避率</t>
+  </si>
+  <si>
+    <t>闪避反击</t>
+  </si>
+  <si>
+    <t>MissGetDamage</t>
+  </si>
+  <si>
+    <t>1|2</t>
+  </si>
+  <si>
+    <t>闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
+  </si>
+  <si>
+    <t>搓牌次数</t>
   </si>
   <si>
     <t>RubbingCardsNum</t>
   </si>
   <si>
-    <t>额外拥有1次搓牌机会</t>
-  </si>
-  <si>
-    <t>暴发户</t>
-  </si>
-  <si>
-    <t>EpicLegendRelicProUp</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>商店刷到史诗及以上品质的圣物概率+10%</t>
-  </si>
-  <si>
-    <t>关系户</t>
-  </si>
-  <si>
-    <t>RelicPricePer</t>
-  </si>
-  <si>
-    <t>商店中的所有圣物的购买价格-20%</t>
-  </si>
-  <si>
-    <t>经济教授</t>
-  </si>
-  <si>
-    <t>GetGoldAfterLevel</t>
-  </si>
-  <si>
-    <t>每关通过后获得的金币数量+30%</t>
-  </si>
-  <si>
-    <t>死灵法师</t>
-  </si>
-  <si>
-    <t>AttackBossDamage</t>
-  </si>
-  <si>
-    <t>对精英、领主造成的伤害+50%</t>
-  </si>
-  <si>
-    <t>裁决使</t>
-  </si>
-  <si>
-    <t>KillingProbabilityTen</t>
-  </si>
-  <si>
-    <t>对血量小于10%的非领主敌人造成伤害时,有20%概率直接斩杀</t>
-  </si>
-  <si>
-    <t>亡命徒</t>
-  </si>
-  <si>
-    <t>HpUnderDamage</t>
-  </si>
-  <si>
-    <t>自身血量小于20%时,造成的伤害+50%</t>
-  </si>
-  <si>
-    <t>囤货王</t>
-  </si>
-  <si>
-    <t>RelicNumMax</t>
-  </si>
-  <si>
-    <t>圣物携带上限+1</t>
-  </si>
-  <si>
-    <t>阴阳师</t>
-  </si>
-  <si>
-    <t>PerspectiveNum</t>
-  </si>
-  <si>
-    <t>每关[透视]使用次数+1</t>
-  </si>
-  <si>
-    <t>营养师</t>
-  </si>
-  <si>
-    <t>HeroHpReplyEveryLevelEnding</t>
-  </si>
-  <si>
-    <t>每回合开始时回复自身2%血量</t>
-  </si>
-  <si>
-    <t>拾荒者</t>
-  </si>
-  <si>
-    <t>KillingGetGold</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,额外获得20金币</t>
-  </si>
-  <si>
-    <t>修炼者</t>
-  </si>
-  <si>
-    <t>KillingGetAttack</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,额外提高2点攻击力</t>
-  </si>
-  <si>
-    <t>决斗大师</t>
-  </si>
-  <si>
-    <t>OneMonsterDamage</t>
-  </si>
-  <si>
-    <t>场上只剩1名敌人时,造成的伤害+50%</t>
-  </si>
-  <si>
-    <t>孩子王</t>
-  </si>
-  <si>
-    <t>ManyMonsterDamage</t>
-  </si>
-  <si>
-    <t>场上敌人多于1名时,造成的伤害+30%</t>
-  </si>
-  <si>
-    <t>急性子</t>
-  </si>
-  <si>
-    <t>FirstShowCardEveryLevel</t>
-  </si>
-  <si>
-    <t>每关首回合比牌时,结算时的倍率+5</t>
+    <t>每关[搓牌]使用次数-1</t>
   </si>
 </sst>
 </file>
@@ -899,9 +905,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1263,451 +1272,541 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.325" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.71666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.34166666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.825" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.325" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.325" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.71666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.4916666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.825" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.3833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.325" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="B5" s="2">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="5" spans="1:7">
+      <c r="B5" s="3">
+        <v>201</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2">
-        <v>-0.25</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="B6" s="2">
-        <v>10002</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="6" spans="1:7">
+      <c r="B6" s="3">
+        <v>202</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="B7" s="2">
-        <v>10003</v>
-      </c>
-      <c r="C7" s="1" t="s">
+    <row r="7" spans="1:7">
+      <c r="B7" s="3"/>
+      <c r="C7" s="2"/>
+      <c r="D7"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" s="3">
+        <v>301</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="2">
-        <v>10004</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="B9" s="4">
+        <v>302</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="2">
-        <v>0.35</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" s="2">
-        <v>10005</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="E9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="B10" s="4">
+        <v>303</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="2">
-        <v>10006</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="4"/>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="3"/>
+      <c r="C11" s="2"/>
+      <c r="D11"/>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="B12" s="4">
+        <v>401</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="1">
+      <c r="D12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="3">
+        <v>402</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="B14" s="4">
+        <v>403</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="3">
+        <v>501</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="B17" s="4">
+        <v>502</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="4">
         <v>150</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="2">
-        <v>10007</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="2">
-        <v>10008</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="2">
-        <v>10009</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" s="2">
-        <v>10010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="F17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="B18" s="3">
+        <v>503</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="B19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="B20" s="3">
+        <v>601</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="3">
+        <v>701</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:7">
+      <c r="B23" s="4">
+        <v>702</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:7">
+      <c r="B24" s="4">
+        <v>703</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="4">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="3"/>
+      <c r="C25" s="2"/>
+      <c r="D25"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="3">
+        <v>801</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-0.25</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:7">
+      <c r="B27" s="4">
+        <v>802</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:7">
+      <c r="B28" s="4">
+        <v>803</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" customFormat="1" spans="1:7">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" spans="1:7">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3">
+        <v>901</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="2">
         <v>-0.2</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="B15" s="2">
-        <v>10011</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="B16" s="2">
-        <v>10012</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:7">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3">
+        <v>902</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="3">
         <v>50</v>
       </c>
-      <c r="E16" s="2">
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:7">
+      <c r="B32" s="4">
+        <v>903</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="5"/>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3">
+        <v>1001</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="3">
         <v>0.5</v>
       </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="2">
-        <v>10013</v>
-      </c>
-      <c r="C17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="2">
-        <v>10014</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="2">
-        <v>10015</v>
-      </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="2">
-        <v>10016</v>
-      </c>
-      <c r="C20" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="3">
-        <v>10017</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="2">
-        <v>10018</v>
-      </c>
-      <c r="C22" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="2">
-        <v>20</v>
-      </c>
-      <c r="F22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="2">
-        <v>10019</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="2">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="2">
-        <v>10020</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="2">
-        <v>10021</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="F34" t="s">
         <v>76</v>
       </c>
-      <c r="D25" t="s">
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3">
+        <v>1002</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="D35" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="2">
-        <v>10022</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="E35" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F35" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="2">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3">
+        <v>1003</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>81</v>
+      </c>
+      <c r="D36" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="3">
+        <v>-1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="10920" windowHeight="11340"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
     <t>HeroTakeDamagePer</t>
   </si>
   <si>
-    <t>受到的伤害+25%</t>
+    <t>受到的伤害+15%</t>
   </si>
   <si>
     <t>攻击追击</t>
@@ -187,7 +187,7 @@
     <t>AoeDamage</t>
   </si>
   <si>
-    <t>攻击时,对所有人造成40%的群体伤害</t>
+    <t>攻击时,对所有人造成50%的群体伤害</t>
   </si>
   <si>
     <t>对精英/领主造成的伤害+50%</t>
@@ -262,7 +262,7 @@
     <t>MissDamagePer</t>
   </si>
   <si>
-    <t>获得50%闪避率</t>
+    <t>获得25%闪避率</t>
   </si>
   <si>
     <t>闪避反击</t>
@@ -1767,7 +1767,7 @@
         <v>75</v>
       </c>
       <c r="E34" s="3">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>

--- a/Config/HeroEntryConfig.xlsx
+++ b/Config/HeroEntryConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10920" windowHeight="11340"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1767,7 +1767,7 @@
         <v>75</v>
       </c>
       <c r="E34" s="3">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F34" t="s">
         <v>76</v>
